--- a/Entrega3_rendimiento_excepcional.xlsx
+++ b/Entrega3_rendimiento_excepcional.xlsx
@@ -1015,7 +1015,7 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
         <v>8</v>
@@ -1027,10 +1027,10 @@
         <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>50.4036</v>
+        <v>46.67</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
         <v>10</v>
@@ -1465,7 +1465,7 @@
         <v>1000</v>
       </c>
       <c r="F23" t="n">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
         <v>1098</v>
@@ -1477,10 +1477,10 @@
         <v>105</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6804</v>
+        <v>0.63</v>
       </c>
       <c r="K23" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
         <v>30</v>
@@ -1510,7 +1510,7 @@
         <v>13</v>
       </c>
       <c r="F24" t="n">
-        <v>12.75</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1525,7 +1525,7 @@
         <v>100</v>
       </c>
       <c r="K24" t="n">
-        <v>14.04</v>
+        <v>13</v>
       </c>
       <c r="L24" t="n">
         <v>15</v>
@@ -1600,7 +1600,7 @@
         <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>10</v>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>20</v>
       </c>
       <c r="M26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1960,7 +1960,7 @@
         <v>1063</v>
       </c>
       <c r="F34" t="n">
-        <v>21.25</v>
+        <v>15</v>
       </c>
       <c r="G34" t="n">
         <v>1080</v>
@@ -1972,16 +1972,16 @@
         <v>42</v>
       </c>
       <c r="J34" t="n">
-        <v>2.4408</v>
+        <v>2.26</v>
       </c>
       <c r="K34" t="n">
-        <v>24.84</v>
+        <v>13</v>
       </c>
       <c r="L34" t="n">
         <v>35</v>
       </c>
       <c r="M34" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -2005,7 +2005,7 @@
         <v>13</v>
       </c>
       <c r="F35" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2017,16 +2017,16 @@
         <v>2</v>
       </c>
       <c r="J35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>14.04</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>15</v>
       </c>
       <c r="M35" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2050,7 +2050,7 @@
         <v>260</v>
       </c>
       <c r="F36" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>280</v>
@@ -2062,16 +2062,16 @@
         <v>40</v>
       </c>
       <c r="J36" t="n">
-        <v>7.203600000000001</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>18.36</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>300</v>
       </c>
       <c r="M36" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2095,7 +2095,7 @@
         <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2107,16 +2107,16 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>20</v>
       </c>
       <c r="M37" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2185,7 +2185,7 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
         <v>1071</v>
       </c>
       <c r="F45" t="n">
-        <v>46.75</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>1060</v>
@@ -2467,16 +2467,16 @@
         <v>44</v>
       </c>
       <c r="J45" t="n">
-        <v>5.3244</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>385</v>
       </c>
       <c r="M45" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2500,7 +2500,7 @@
         <v>13</v>
       </c>
       <c r="F46" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2512,16 +2512,16 @@
         <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>14.04</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>15</v>
       </c>
       <c r="M46" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2545,7 +2545,7 @@
         <v>260</v>
       </c>
       <c r="F47" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>220</v>
@@ -2557,16 +2557,16 @@
         <v>40</v>
       </c>
       <c r="J47" t="n">
-        <v>28.8036</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>74.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>300</v>
       </c>
       <c r="M47" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2590,7 +2590,7 @@
         <v>20</v>
       </c>
       <c r="F48" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>20</v>
       </c>
       <c r="M48" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2635,7 +2635,7 @@
         <v>150</v>
       </c>
       <c r="F49" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>130</v>
@@ -2647,16 +2647,16 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>14.3964</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>100</v>
       </c>
       <c r="M49" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2680,7 +2680,7 @@
         <v>48</v>
       </c>
       <c r="F50" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>30</v>
@@ -2692,16 +2692,16 @@
         <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>43.2</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>20.52</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>50</v>
       </c>
       <c r="M50" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2746,7 +2746,7 @@
         <v>60</v>
       </c>
       <c r="M51" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2950,7 +2950,7 @@
         <v>1071</v>
       </c>
       <c r="F56" t="n">
-        <v>131.75</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>1000</v>
@@ -2962,16 +2962,16 @@
         <v>84</v>
       </c>
       <c r="J56" t="n">
-        <v>14.4936</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>153.36</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>545</v>
       </c>
       <c r="M56" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2995,7 +2995,7 @@
         <v>13</v>
       </c>
       <c r="F57" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -3007,16 +3007,16 @@
         <v>2</v>
       </c>
       <c r="J57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>14.04</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>15</v>
       </c>
       <c r="M57" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3040,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="F58" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>140</v>
@@ -3052,16 +3052,16 @@
         <v>40</v>
       </c>
       <c r="J58" t="n">
-        <v>57.5964</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>150.12</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>300</v>
       </c>
       <c r="M58" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3085,7 +3085,7 @@
         <v>20</v>
       </c>
       <c r="F59" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -3097,16 +3097,16 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>20</v>
       </c>
       <c r="M59" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3130,7 +3130,7 @@
         <v>150</v>
       </c>
       <c r="F60" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>110</v>
@@ -3142,16 +3142,16 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>38.1132</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>57.24</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>170</v>
       </c>
       <c r="M60" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3175,7 +3175,7 @@
         <v>48</v>
       </c>
       <c r="F61" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
         <v>10</v>
@@ -3187,16 +3187,16 @@
         <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>86.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>41.04000000000001</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>50</v>
       </c>
       <c r="M61" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3220,7 +3220,7 @@
         <v>180</v>
       </c>
       <c r="F62" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>140</v>
@@ -3232,16 +3232,16 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>23.9976</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>43.2</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>120</v>
       </c>
       <c r="M62" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3265,7 +3265,7 @@
         <v>190</v>
       </c>
       <c r="F63" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>190</v>
@@ -3277,16 +3277,16 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>120</v>
       </c>
       <c r="M63" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3445,7 +3445,7 @@
         <v>1101</v>
       </c>
       <c r="F67" t="n">
-        <v>293.25</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>830</v>
@@ -3457,16 +3457,16 @@
         <v>74</v>
       </c>
       <c r="J67" t="n">
-        <v>31.7088</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>338.04</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>795</v>
       </c>
       <c r="M67" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3490,7 +3490,7 @@
         <v>13</v>
       </c>
       <c r="F68" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -3502,16 +3502,16 @@
         <v>2</v>
       </c>
       <c r="J68" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>14.04</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>15</v>
       </c>
       <c r="M68" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3535,7 +3535,7 @@
         <v>260</v>
       </c>
       <c r="F69" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>100</v>
@@ -3547,16 +3547,16 @@
         <v>40</v>
       </c>
       <c r="J69" t="n">
-        <v>72.00360000000001</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>186.84</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>300</v>
       </c>
       <c r="M69" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3580,7 +3580,7 @@
         <v>20</v>
       </c>
       <c r="F70" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -3592,16 +3592,16 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
         <v>20</v>
       </c>
       <c r="M70" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3625,7 +3625,7 @@
         <v>160</v>
       </c>
       <c r="F71" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
@@ -3637,16 +3637,16 @@
         <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>63.5256</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>101.52</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
         <v>170</v>
       </c>
       <c r="M71" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3670,7 +3670,7 @@
         <v>48</v>
       </c>
       <c r="F72" t="n">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3682,16 +3682,16 @@
         <v>2</v>
       </c>
       <c r="J72" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>51.84</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>50</v>
       </c>
       <c r="M72" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -3715,7 +3715,7 @@
         <v>180</v>
       </c>
       <c r="F73" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
         <v>105</v>
@@ -3727,16 +3727,16 @@
         <v>5</v>
       </c>
       <c r="J73" t="n">
-        <v>46.6992</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>84.24000000000001</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>185</v>
       </c>
       <c r="M73" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3760,7 +3760,7 @@
         <v>190</v>
       </c>
       <c r="F74" t="n">
-        <v>59.5</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>130</v>
@@ -3772,16 +3772,16 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>37.8</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>72.36</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
         <v>120</v>
       </c>
       <c r="M74" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3805,7 +3805,7 @@
         <v>120</v>
       </c>
       <c r="F75" t="n">
-        <v>21.25</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>95</v>
@@ -3817,16 +3817,16 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>22.4964</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
         <v>120</v>
       </c>
       <c r="M75" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3940,7 +3940,7 @@
         <v>1111</v>
       </c>
       <c r="F78" t="n">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>620</v>
@@ -3952,16 +3952,16 @@
         <v>69</v>
       </c>
       <c r="J78" t="n">
-        <v>51.25680000000001</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>559.4400000000001</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
         <v>980</v>
       </c>
       <c r="M78" t="n">
-        <v>532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -3985,7 +3985,7 @@
         <v>13</v>
       </c>
       <c r="F79" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3997,16 +3997,16 @@
         <v>2</v>
       </c>
       <c r="J79" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>14.04</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
         <v>15</v>
       </c>
       <c r="M79" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4030,7 +4030,7 @@
         <v>260</v>
       </c>
       <c r="F80" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>20</v>
@@ -4042,16 +4042,16 @@
         <v>40</v>
       </c>
       <c r="J80" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>262.44</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
         <v>300</v>
       </c>
       <c r="M80" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -4075,7 +4075,7 @@
         <v>20</v>
       </c>
       <c r="F81" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -4087,16 +4087,16 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
         <v>20</v>
       </c>
       <c r="M81" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -4120,7 +4120,7 @@
         <v>160</v>
       </c>
       <c r="F82" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>30</v>
@@ -4132,16 +4132,16 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>88.938</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>142.56</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>170</v>
       </c>
       <c r="M82" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -4165,7 +4165,7 @@
         <v>63</v>
       </c>
       <c r="F83" t="n">
-        <v>46.75</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>10</v>
@@ -4177,16 +4177,16 @@
         <v>2</v>
       </c>
       <c r="J83" t="n">
-        <v>91.38960000000002</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>57.24</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
         <v>65</v>
       </c>
       <c r="M83" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -4210,7 +4210,7 @@
         <v>180</v>
       </c>
       <c r="F84" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
         <v>65</v>
@@ -4222,16 +4222,16 @@
         <v>5</v>
       </c>
       <c r="J84" t="n">
-        <v>70.0488</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>126.36</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
         <v>185</v>
       </c>
       <c r="M84" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -4255,7 +4255,7 @@
         <v>190</v>
       </c>
       <c r="F85" t="n">
-        <v>106.25</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
         <v>85</v>
@@ -4267,16 +4267,16 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>64.28160000000001</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>122.04</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>210</v>
       </c>
       <c r="M85" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -4300,7 +4300,7 @@
         <v>120</v>
       </c>
       <c r="F86" t="n">
-        <v>38.25</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
         <v>75</v>
@@ -4312,16 +4312,16 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>40.5</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>48.6</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
         <v>120</v>
       </c>
       <c r="M86" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -4435,7 +4435,7 @@
         <v>1126</v>
       </c>
       <c r="F89" t="n">
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>405</v>
@@ -4447,16 +4447,16 @@
         <v>79</v>
       </c>
       <c r="J89" t="n">
-        <v>71.7012</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>794.8800000000001</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>1085</v>
       </c>
       <c r="M89" t="n">
-        <v>799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4480,7 +4480,7 @@
         <v>13</v>
       </c>
       <c r="F90" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -4492,16 +4492,16 @@
         <v>2</v>
       </c>
       <c r="J90" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>14.04</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
         <v>15</v>
       </c>
       <c r="M90" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -4525,7 +4525,7 @@
         <v>260</v>
       </c>
       <c r="F91" t="n">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -4537,16 +4537,16 @@
         <v>60</v>
       </c>
       <c r="J91" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>280.8</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
         <v>320</v>
       </c>
       <c r="M91" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -4570,7 +4570,7 @@
         <v>20</v>
       </c>
       <c r="F92" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -4582,16 +4582,16 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>20</v>
       </c>
       <c r="M92" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4615,7 +4615,7 @@
         <v>160</v>
       </c>
       <c r="F93" t="n">
-        <v>144.5</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -4627,16 +4627,16 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>172.8</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
         <v>170</v>
       </c>
       <c r="M93" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -4660,7 +4660,7 @@
         <v>63</v>
       </c>
       <c r="F94" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>5</v>
@@ -4672,16 +4672,16 @@
         <v>2</v>
       </c>
       <c r="J94" t="n">
-        <v>99.69480000000001</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>62.64</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
         <v>65</v>
       </c>
       <c r="M94" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4705,7 +4705,7 @@
         <v>180</v>
       </c>
       <c r="F95" t="n">
-        <v>144.5</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>15</v>
@@ -4717,16 +4717,16 @@
         <v>5</v>
       </c>
       <c r="J95" t="n">
-        <v>99.24120000000001</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>178.2</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
         <v>185</v>
       </c>
       <c r="M95" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4750,7 +4750,7 @@
         <v>190</v>
       </c>
       <c r="F96" t="n">
-        <v>148.75</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
         <v>35</v>
@@ -4762,16 +4762,16 @@
         <v>20</v>
       </c>
       <c r="J96" t="n">
-        <v>89.99640000000001</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>170.64</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>210</v>
       </c>
       <c r="M96" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4795,7 +4795,7 @@
         <v>120</v>
       </c>
       <c r="F97" t="n">
-        <v>72.25</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
         <v>35</v>
@@ -4807,16 +4807,16 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>76.49640000000001</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>91.80000000000001</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
         <v>120</v>
       </c>
       <c r="M97" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -4930,7 +4930,7 @@
         <v>1126</v>
       </c>
       <c r="F100" t="n">
-        <v>862.75</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
         <v>210</v>
@@ -4942,16 +4942,16 @@
         <v>99</v>
       </c>
       <c r="J100" t="n">
-        <v>89.48880000000001</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>993.6</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
         <v>1105</v>
       </c>
       <c r="M100" t="n">
-        <v>933</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -4975,7 +4975,7 @@
         <v>13</v>
       </c>
       <c r="F101" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4987,16 +4987,16 @@
         <v>2</v>
       </c>
       <c r="J101" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>14.04</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
         <v>15</v>
       </c>
       <c r="M101" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -5020,7 +5020,7 @@
         <v>260</v>
       </c>
       <c r="F102" t="n">
-        <v>263.5</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -5032,16 +5032,16 @@
         <v>50</v>
       </c>
       <c r="J102" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>280.8</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
         <v>310</v>
       </c>
       <c r="M102" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -5065,7 +5065,7 @@
         <v>20</v>
       </c>
       <c r="F103" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -5077,16 +5077,16 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="L103" t="n">
         <v>20</v>
       </c>
       <c r="M103" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -5110,7 +5110,7 @@
         <v>160</v>
       </c>
       <c r="F104" t="n">
-        <v>144.5</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -5122,16 +5122,16 @@
         <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>172.8</v>
+        <v>0</v>
       </c>
       <c r="L104" t="n">
         <v>170</v>
       </c>
       <c r="M104" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -5155,7 +5155,7 @@
         <v>63</v>
       </c>
       <c r="F105" t="n">
-        <v>53.55</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
         <v>2</v>
@@ -5167,16 +5167,16 @@
         <v>2</v>
       </c>
       <c r="J105" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>65.88000000000001</v>
+        <v>0</v>
       </c>
       <c r="L105" t="n">
         <v>65</v>
       </c>
       <c r="M105" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -5200,7 +5200,7 @@
         <v>180</v>
       </c>
       <c r="F106" t="n">
-        <v>157.25</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -5212,16 +5212,16 @@
         <v>5</v>
       </c>
       <c r="J106" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>194.4</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
         <v>185</v>
       </c>
       <c r="M106" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -5245,7 +5245,7 @@
         <v>190</v>
       </c>
       <c r="F107" t="n">
-        <v>191.25</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
         <v>15</v>
@@ -5257,16 +5257,16 @@
         <v>50</v>
       </c>
       <c r="J107" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>192.24</v>
+        <v>0</v>
       </c>
       <c r="L107" t="n">
         <v>240</v>
       </c>
       <c r="M107" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -5290,7 +5290,7 @@
         <v>120</v>
       </c>
       <c r="F108" t="n">
-        <v>97.75</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
         <v>5</v>
@@ -5302,16 +5302,16 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>124.2</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
         <v>120</v>
       </c>
       <c r="M108" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -5335,7 +5335,7 @@
         <v>80</v>
       </c>
       <c r="F109" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
         <v>70</v>
@@ -5347,16 +5347,16 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="L109" t="n">
         <v>80</v>
       </c>
       <c r="M109" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -5425,7 +5425,7 @@
         <v>1126</v>
       </c>
       <c r="F111" t="n">
-        <v>946.05</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
         <v>132</v>
@@ -5437,16 +5437,16 @@
         <v>119</v>
       </c>
       <c r="J111" t="n">
-        <v>96.55200000000001</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>1076.76</v>
+        <v>0</v>
       </c>
       <c r="L111" t="n">
         <v>1205</v>
       </c>
       <c r="M111" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -5470,7 +5470,7 @@
         <v>13</v>
       </c>
       <c r="F112" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -5482,16 +5482,16 @@
         <v>2</v>
       </c>
       <c r="J112" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>14.04</v>
+        <v>0</v>
       </c>
       <c r="L112" t="n">
         <v>15</v>
       </c>
       <c r="M112" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5515,7 +5515,7 @@
         <v>260</v>
       </c>
       <c r="F113" t="n">
-        <v>263.5</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -5527,16 +5527,16 @@
         <v>50</v>
       </c>
       <c r="J113" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>280.8</v>
+        <v>0</v>
       </c>
       <c r="L113" t="n">
         <v>310</v>
       </c>
       <c r="M113" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -5560,7 +5560,7 @@
         <v>20</v>
       </c>
       <c r="F114" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -5572,16 +5572,16 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="L114" t="n">
         <v>20</v>
       </c>
       <c r="M114" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -5605,7 +5605,7 @@
         <v>160</v>
       </c>
       <c r="F115" t="n">
-        <v>144.5</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -5617,16 +5617,16 @@
         <v>10</v>
       </c>
       <c r="J115" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>172.8</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
         <v>170</v>
       </c>
       <c r="M115" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5650,7 +5650,7 @@
         <v>63</v>
       </c>
       <c r="F116" t="n">
-        <v>57.8</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -5662,16 +5662,16 @@
         <v>5</v>
       </c>
       <c r="J116" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>68.04000000000001</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
         <v>68</v>
       </c>
       <c r="M116" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -5695,7 +5695,7 @@
         <v>180</v>
       </c>
       <c r="F117" t="n">
-        <v>157.25</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -5707,16 +5707,16 @@
         <v>5</v>
       </c>
       <c r="J117" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>194.4</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
         <v>185</v>
       </c>
       <c r="M117" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -5740,7 +5740,7 @@
         <v>190</v>
       </c>
       <c r="F118" t="n">
-        <v>199.75</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
         <v>5</v>
@@ -5752,16 +5752,16 @@
         <v>50</v>
       </c>
       <c r="J118" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>200.88</v>
+        <v>0</v>
       </c>
       <c r="L118" t="n">
         <v>240</v>
       </c>
       <c r="M118" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -5785,7 +5785,7 @@
         <v>120</v>
       </c>
       <c r="F119" t="n">
-        <v>114.75</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
         <v>5</v>
@@ -5797,16 +5797,16 @@
         <v>20</v>
       </c>
       <c r="J119" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>125.28</v>
+        <v>0</v>
       </c>
       <c r="L119" t="n">
         <v>140</v>
       </c>
       <c r="M119" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -5830,7 +5830,7 @@
         <v>80</v>
       </c>
       <c r="F120" t="n">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
         <v>30</v>
@@ -5842,16 +5842,16 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L120" t="n">
         <v>80</v>
       </c>
       <c r="M120" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -5875,7 +5875,7 @@
         <v>25</v>
       </c>
       <c r="F121" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
         <v>20</v>
@@ -5887,16 +5887,16 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="L121" t="n">
         <v>25</v>
       </c>
       <c r="M121" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -5920,7 +5920,7 @@
         <v>1111</v>
       </c>
       <c r="F122" t="n">
-        <v>1014.05</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>60</v>
@@ -5932,16 +5932,16 @@
         <v>142</v>
       </c>
       <c r="J122" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>1137.24</v>
+        <v>0</v>
       </c>
       <c r="L122" t="n">
         <v>1253</v>
       </c>
       <c r="M122" t="n">
-        <v>1152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -5965,7 +5965,7 @@
         <v>13</v>
       </c>
       <c r="F123" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -5977,16 +5977,16 @@
         <v>2</v>
       </c>
       <c r="J123" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>14.04</v>
+        <v>0</v>
       </c>
       <c r="L123" t="n">
         <v>15</v>
       </c>
       <c r="M123" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -6010,7 +6010,7 @@
         <v>260</v>
       </c>
       <c r="F124" t="n">
-        <v>263.5</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -6022,16 +6022,16 @@
         <v>50</v>
       </c>
       <c r="J124" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>280.8</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
         <v>310</v>
       </c>
       <c r="M124" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -6055,7 +6055,7 @@
         <v>20</v>
       </c>
       <c r="F125" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -6067,16 +6067,16 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="L125" t="n">
         <v>20</v>
       </c>
       <c r="M125" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -6100,7 +6100,7 @@
         <v>160</v>
       </c>
       <c r="F126" t="n">
-        <v>144.5</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -6112,16 +6112,16 @@
         <v>10</v>
       </c>
       <c r="J126" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>172.8</v>
+        <v>0</v>
       </c>
       <c r="L126" t="n">
         <v>170</v>
       </c>
       <c r="M126" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -6145,7 +6145,7 @@
         <v>63</v>
       </c>
       <c r="F127" t="n">
-        <v>57.8</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -6157,16 +6157,16 @@
         <v>5</v>
       </c>
       <c r="J127" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>68.04000000000001</v>
+        <v>0</v>
       </c>
       <c r="L127" t="n">
         <v>68</v>
       </c>
       <c r="M127" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -6190,7 +6190,7 @@
         <v>180</v>
       </c>
       <c r="F128" t="n">
-        <v>157.25</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -6202,16 +6202,16 @@
         <v>5</v>
       </c>
       <c r="J128" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>194.4</v>
+        <v>0</v>
       </c>
       <c r="L128" t="n">
         <v>185</v>
       </c>
       <c r="M128" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -6235,7 +6235,7 @@
         <v>190</v>
       </c>
       <c r="F129" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -6247,16 +6247,16 @@
         <v>50</v>
       </c>
       <c r="J129" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>205.2</v>
+        <v>0</v>
       </c>
       <c r="L129" t="n">
         <v>240</v>
       </c>
       <c r="M129" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -6280,7 +6280,7 @@
         <v>120</v>
       </c>
       <c r="F130" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -6292,16 +6292,16 @@
         <v>20</v>
       </c>
       <c r="J130" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="L130" t="n">
         <v>140</v>
       </c>
       <c r="M130" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -6325,7 +6325,7 @@
         <v>80</v>
       </c>
       <c r="F131" t="n">
-        <v>59.5</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
         <v>10</v>
@@ -6337,16 +6337,16 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>94.5</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>75.60000000000001</v>
+        <v>0</v>
       </c>
       <c r="L131" t="n">
         <v>80</v>
       </c>
       <c r="M131" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -6370,7 +6370,7 @@
         <v>25</v>
       </c>
       <c r="F132" t="n">
-        <v>11.05</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
         <v>12</v>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>56.16</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>14.04</v>
+        <v>0</v>
       </c>
       <c r="L132" t="n">
         <v>25</v>
       </c>
       <c r="M132" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -6415,7 +6415,7 @@
         <v>1111</v>
       </c>
       <c r="F133" t="n">
-        <v>1046.35</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
         <v>22</v>
@@ -6427,16 +6427,16 @@
         <v>142</v>
       </c>
       <c r="J133" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>1176.12</v>
+        <v>0</v>
       </c>
       <c r="L133" t="n">
         <v>1253</v>
       </c>
       <c r="M133" t="n">
-        <v>1185</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6531,7 +6531,7 @@
         <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>12.75</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
         <v>260</v>
       </c>
       <c r="E3" t="n">
-        <v>263.5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -6583,16 +6583,16 @@
         <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>310</v>
       </c>
       <c r="L3" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -6611,7 +6611,7 @@
         <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -6623,16 +6623,16 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>20</v>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -6651,7 +6651,7 @@
         <v>160</v>
       </c>
       <c r="E5" t="n">
-        <v>144.5</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -6663,16 +6663,16 @@
         <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>170</v>
       </c>
       <c r="L5" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6691,7 +6691,7 @@
         <v>66</v>
       </c>
       <c r="E6" t="n">
-        <v>57.8</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -6703,16 +6703,16 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>68</v>
       </c>
       <c r="L6" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6731,7 +6731,7 @@
         <v>180</v>
       </c>
       <c r="E7" t="n">
-        <v>157.25</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -6743,16 +6743,16 @@
         <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>185</v>
       </c>
       <c r="L7" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6771,7 +6771,7 @@
         <v>190</v>
       </c>
       <c r="E8" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -6783,16 +6783,16 @@
         <v>50</v>
       </c>
       <c r="I8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>240</v>
       </c>
       <c r="L8" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6811,7 +6811,7 @@
         <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>123.25</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6823,16 +6823,16 @@
         <v>25</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>145</v>
       </c>
       <c r="L9" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6851,7 +6851,7 @@
         <v>80</v>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -6863,16 +6863,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>80</v>
       </c>
       <c r="L10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6891,7 +6891,7 @@
         <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>21.25</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -6903,16 +6903,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6931,7 +6931,7 @@
         <v>1114</v>
       </c>
       <c r="E12" t="n">
-        <v>1069.3</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6943,16 +6943,16 @@
         <v>144</v>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
-        <v>1114</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
         <v>1258</v>
       </c>
       <c r="L12" t="n">
-        <v>1207</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -7063,25 +7063,25 @@
         <v>1000</v>
       </c>
       <c r="C3" t="n">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6804</v>
+        <v>0.63</v>
       </c>
       <c r="F3" t="n">
-        <v>-994.6</v>
+        <v>-995</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0054</v>
+        <v>0.005</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5499999999999998</v>
+        <v>-2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.907563025210084</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="J3" t="n">
         <v>2000</v>
@@ -7097,25 +7097,25 @@
         <v>1063</v>
       </c>
       <c r="C4" t="n">
-        <v>21.25</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>24.84</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4408</v>
+        <v>2.26</v>
       </c>
       <c r="F4" t="n">
-        <v>-1038.16</v>
+        <v>-1050</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02336782690498589</v>
+        <v>0.01222953904045155</v>
       </c>
       <c r="H4" t="n">
-        <v>3.590000000000003</v>
+        <v>-2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.168941176470588</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="J4" t="n">
         <v>462.9629629629629</v>
@@ -7131,25 +7131,25 @@
         <v>1071</v>
       </c>
       <c r="C5" t="n">
-        <v>46.75</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3244</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-1017</v>
+        <v>-1021</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05042016806722689</v>
+        <v>0.0467</v>
       </c>
       <c r="H5" t="n">
-        <v>7.25</v>
+        <v>-5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.155080213903743</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="J5" t="n">
         <v>214.1327623126338</v>
@@ -7165,25 +7165,25 @@
         <v>1071</v>
       </c>
       <c r="C6" t="n">
-        <v>131.75</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>153.36</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>14.4936</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-917.64</v>
+        <v>-929</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1431932773109244</v>
+        <v>0.1326</v>
       </c>
       <c r="H6" t="n">
-        <v>21.61000000000001</v>
+        <v>-13</v>
       </c>
       <c r="I6" t="n">
-        <v>1.164022770398482</v>
+        <v>0.9161290322580645</v>
       </c>
       <c r="J6" t="n">
         <v>75.41478129713424</v>
@@ -7199,25 +7199,25 @@
         <v>1101</v>
       </c>
       <c r="C7" t="n">
-        <v>293.25</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>338.04</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>31.7088</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-762.96</v>
+        <v>-788</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3070299727520436</v>
+        <v>0.2843</v>
       </c>
       <c r="H7" t="n">
-        <v>44.79000000000002</v>
+        <v>-32</v>
       </c>
       <c r="I7" t="n">
-        <v>1.152736572890026</v>
+        <v>0.9072463768115943</v>
       </c>
       <c r="J7" t="n">
         <v>35.1741118536757</v>
@@ -7233,25 +7233,25 @@
         <v>1111</v>
       </c>
       <c r="C8" t="n">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>559.4400000000001</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>51.25680000000001</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-551.5599999999999</v>
+        <v>-593</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5035463546354636</v>
+        <v>0.4662</v>
       </c>
       <c r="H8" t="n">
-        <v>83.44000000000005</v>
+        <v>-42</v>
       </c>
       <c r="I8" t="n">
-        <v>1.175294117647059</v>
+        <v>0.925</v>
       </c>
       <c r="J8" t="n">
         <v>21.45002145002145</v>
@@ -7267,25 +7267,25 @@
         <v>1126</v>
       </c>
       <c r="C9" t="n">
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>794.8800000000001</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>71.7012</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-331.1199999999999</v>
+        <v>-390</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7059325044404975</v>
+        <v>0.6536</v>
       </c>
       <c r="H9" t="n">
-        <v>114.8800000000001</v>
+        <v>-64</v>
       </c>
       <c r="I9" t="n">
-        <v>1.168941176470588</v>
+        <v>0.92</v>
       </c>
       <c r="J9" t="n">
         <v>15.29987760097919</v>
@@ -7301,25 +7301,25 @@
         <v>1126</v>
       </c>
       <c r="C10" t="n">
-        <v>862.75</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>993.6</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>89.48880000000001</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-132.4</v>
+        <v>-206</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8824156305506217</v>
+        <v>0.8171</v>
       </c>
       <c r="H10" t="n">
-        <v>130.85</v>
+        <v>-95</v>
       </c>
       <c r="I10" t="n">
-        <v>1.151666183714865</v>
+        <v>0.9064039408866995</v>
       </c>
       <c r="J10" t="n">
         <v>12.23840411210378</v>
@@ -7335,25 +7335,25 @@
         <v>1126</v>
       </c>
       <c r="C11" t="n">
-        <v>946.05</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1076.76</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>96.55200000000001</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-49.24000000000001</v>
+        <v>-129</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9562699822380106</v>
+        <v>0.8854</v>
       </c>
       <c r="H11" t="n">
-        <v>130.71</v>
+        <v>-116</v>
       </c>
       <c r="I11" t="n">
-        <v>1.138163944823212</v>
+        <v>0.8957771787960467</v>
       </c>
       <c r="J11" t="n">
         <v>11.2943302462164</v>
@@ -7369,25 +7369,25 @@
         <v>1111</v>
       </c>
       <c r="C12" t="n">
-        <v>1014.05</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1137.24</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>26.24000000000001</v>
+        <v>-58</v>
       </c>
       <c r="G12" t="n">
-        <v>1.023618361836184</v>
+        <v>0.9478</v>
       </c>
       <c r="H12" t="n">
-        <v>123.1900000000001</v>
+        <v>-140</v>
       </c>
       <c r="I12" t="n">
-        <v>1.121483161579804</v>
+        <v>0.8826487845766974</v>
       </c>
       <c r="J12" t="n">
         <v>10.55074910318633</v>
@@ -7403,25 +7403,25 @@
         <v>1111</v>
       </c>
       <c r="C13" t="n">
-        <v>1046.35</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1176.12</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>65.12000000000012</v>
+        <v>-22</v>
       </c>
       <c r="G13" t="n">
-        <v>1.058613861386139</v>
+        <v>0.9802</v>
       </c>
       <c r="H13" t="n">
-        <v>129.7700000000002</v>
+        <v>-142</v>
       </c>
       <c r="I13" t="n">
-        <v>1.124021598891385</v>
+        <v>0.8846466287571081</v>
       </c>
       <c r="J13" t="n">
         <v>10.20199959192002</v>
@@ -8020,7 +8020,7 @@
         <v>1000</v>
       </c>
       <c r="F3" t="n">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
         <v>1098</v>
@@ -8032,10 +8032,10 @@
         <v>105</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6804</v>
+        <v>0.63</v>
       </c>
       <c r="K3" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
         <v>30</v>
@@ -8065,7 +8065,7 @@
         <v>1063</v>
       </c>
       <c r="F4" t="n">
-        <v>21.25</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
         <v>1080</v>
@@ -8077,16 +8077,16 @@
         <v>42</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4408</v>
+        <v>2.26</v>
       </c>
       <c r="K4" t="n">
-        <v>24.84</v>
+        <v>13</v>
       </c>
       <c r="L4" t="n">
         <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -8110,7 +8110,7 @@
         <v>1071</v>
       </c>
       <c r="F5" t="n">
-        <v>46.75</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>1060</v>
@@ -8122,16 +8122,16 @@
         <v>44</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3244</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>385</v>
       </c>
       <c r="M5" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8155,7 +8155,7 @@
         <v>1071</v>
       </c>
       <c r="F6" t="n">
-        <v>131.75</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
@@ -8167,16 +8167,16 @@
         <v>84</v>
       </c>
       <c r="J6" t="n">
-        <v>14.4936</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>153.36</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>545</v>
       </c>
       <c r="M6" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8200,7 +8200,7 @@
         <v>1101</v>
       </c>
       <c r="F7" t="n">
-        <v>293.25</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>830</v>
@@ -8212,16 +8212,16 @@
         <v>74</v>
       </c>
       <c r="J7" t="n">
-        <v>31.7088</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>338.04</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>795</v>
       </c>
       <c r="M7" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8245,7 +8245,7 @@
         <v>1111</v>
       </c>
       <c r="F8" t="n">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>620</v>
@@ -8257,16 +8257,16 @@
         <v>69</v>
       </c>
       <c r="J8" t="n">
-        <v>51.25680000000001</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>559.4400000000001</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>980</v>
       </c>
       <c r="M8" t="n">
-        <v>532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -8290,7 +8290,7 @@
         <v>1126</v>
       </c>
       <c r="F9" t="n">
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>405</v>
@@ -8302,16 +8302,16 @@
         <v>79</v>
       </c>
       <c r="J9" t="n">
-        <v>71.7012</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>794.8800000000001</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>1085</v>
       </c>
       <c r="M9" t="n">
-        <v>799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -8335,7 +8335,7 @@
         <v>1126</v>
       </c>
       <c r="F10" t="n">
-        <v>862.75</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>210</v>
@@ -8347,16 +8347,16 @@
         <v>99</v>
       </c>
       <c r="J10" t="n">
-        <v>89.48880000000001</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>993.6</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1105</v>
       </c>
       <c r="M10" t="n">
-        <v>933</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -8380,7 +8380,7 @@
         <v>1126</v>
       </c>
       <c r="F11" t="n">
-        <v>946.05</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>132</v>
@@ -8392,16 +8392,16 @@
         <v>119</v>
       </c>
       <c r="J11" t="n">
-        <v>96.55200000000001</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1076.76</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>1205</v>
       </c>
       <c r="M11" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -8425,7 +8425,7 @@
         <v>1111</v>
       </c>
       <c r="F12" t="n">
-        <v>1014.05</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -8437,16 +8437,16 @@
         <v>142</v>
       </c>
       <c r="J12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1137.24</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>1253</v>
       </c>
       <c r="M12" t="n">
-        <v>1152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -8470,7 +8470,7 @@
         <v>1111</v>
       </c>
       <c r="F13" t="n">
-        <v>1046.35</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>22</v>
@@ -8482,16 +8482,16 @@
         <v>142</v>
       </c>
       <c r="J13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1176.12</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>1253</v>
       </c>
       <c r="M13" t="n">
-        <v>1185</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
